--- a/Galar_Pokemon_Locations.xlsx
+++ b/Galar_Pokemon_Locations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G829"/>
+  <dimension ref="A1:H829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>% of appearance</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>1st?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -483,6 +488,11 @@
       <c r="G2" t="n">
         <v>60</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -514,6 +524,11 @@
       <c r="G3" t="n">
         <v>20</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -545,6 +560,11 @@
       <c r="G4" t="n">
         <v>20</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -576,6 +596,11 @@
       <c r="G5" t="n">
         <v>25</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -607,6 +632,11 @@
       <c r="G6" t="n">
         <v>15</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>12.5</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -669,6 +704,11 @@
       <c r="G8" t="n">
         <v>10</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -700,6 +740,11 @@
       <c r="G9" t="n">
         <v>10</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -731,6 +776,11 @@
       <c r="G10" t="n">
         <v>7.5</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -762,6 +812,11 @@
       <c r="G11" t="n">
         <v>7.5</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -793,6 +848,11 @@
       <c r="G12" t="n">
         <v>5</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -824,6 +884,11 @@
       <c r="G13" t="n">
         <v>2.5</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -855,6 +920,11 @@
       <c r="G14" t="n">
         <v>2.5</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -886,6 +956,11 @@
       <c r="G15" t="n">
         <v>2.5</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -917,6 +992,11 @@
       <c r="G16" t="n">
         <v>29.03</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -948,6 +1028,11 @@
       <c r="G17" t="n">
         <v>19.35</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -979,6 +1064,11 @@
       <c r="G18" t="n">
         <v>19.35</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1010,6 +1100,11 @@
       <c r="G19" t="n">
         <v>9.68</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1041,6 +1136,11 @@
       <c r="G20" t="n">
         <v>9.68</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1072,6 +1172,11 @@
       <c r="G21" t="n">
         <v>6.45</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1103,6 +1208,11 @@
       <c r="G22" t="n">
         <v>3.23</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1134,6 +1244,11 @@
       <c r="G23" t="n">
         <v>3.23</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1165,6 +1280,11 @@
       <c r="G24" t="n">
         <v>80</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1196,6 +1316,11 @@
       <c r="G25" t="n">
         <v>15</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1227,6 +1352,11 @@
       <c r="G26" t="n">
         <v>5</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1258,6 +1388,11 @@
       <c r="G27" t="n">
         <v>70</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1289,6 +1424,11 @@
       <c r="G28" t="n">
         <v>28</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1320,6 +1460,11 @@
       <c r="G29" t="n">
         <v>2</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1351,6 +1496,11 @@
       <c r="G30" t="n">
         <v>20.78</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1382,6 +1532,11 @@
       <c r="G31" t="n">
         <v>19.74</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1413,6 +1568,11 @@
       <c r="G32" t="n">
         <v>14.29</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1444,6 +1604,11 @@
       <c r="G33" t="n">
         <v>10.39</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1475,6 +1640,11 @@
       <c r="G34" t="n">
         <v>10.39</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1506,6 +1676,11 @@
       <c r="G35" t="n">
         <v>7.79</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1537,6 +1712,11 @@
       <c r="G36" t="n">
         <v>5.19</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1568,6 +1748,11 @@
       <c r="G37" t="n">
         <v>5.19</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1599,6 +1784,11 @@
       <c r="G38" t="n">
         <v>2.6</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1630,6 +1820,11 @@
       <c r="G39" t="n">
         <v>2.6</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1661,6 +1856,11 @@
       <c r="G40" t="n">
         <v>1.04</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1692,6 +1892,11 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1723,6 +1928,11 @@
       <c r="G42" t="n">
         <v>20</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1754,6 +1964,11 @@
       <c r="G43" t="n">
         <v>29.21</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1785,6 +2000,11 @@
       <c r="G44" t="n">
         <v>26.97</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1816,6 +2036,11 @@
       <c r="G45" t="n">
         <v>16.85</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1847,6 +2072,11 @@
       <c r="G46" t="n">
         <v>13.48</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1878,6 +2108,11 @@
       <c r="G47" t="n">
         <v>6.74</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1909,6 +2144,11 @@
       <c r="G48" t="n">
         <v>3.37</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1940,6 +2180,11 @@
       <c r="G49" t="n">
         <v>3.37</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1971,6 +2216,11 @@
       <c r="G50" t="n">
         <v>70</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2002,6 +2252,11 @@
       <c r="G51" t="n">
         <v>30</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2033,6 +2288,11 @@
       <c r="G52" t="n">
         <v>35.82</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2064,6 +2324,11 @@
       <c r="G53" t="n">
         <v>23.88</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2095,6 +2360,11 @@
       <c r="G54" t="n">
         <v>17.91</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2126,6 +2396,11 @@
       <c r="G55" t="n">
         <v>11.94</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2157,6 +2432,11 @@
       <c r="G56" t="n">
         <v>4.48</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2188,6 +2468,11 @@
       <c r="G57" t="n">
         <v>2.99</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2219,6 +2504,11 @@
       <c r="G58" t="n">
         <v>2.99</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2250,6 +2540,11 @@
       <c r="G59" t="n">
         <v>50</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2281,6 +2576,11 @@
       <c r="G60" t="n">
         <v>50</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2312,6 +2612,11 @@
       <c r="G61" t="n">
         <v>30</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2343,6 +2648,11 @@
       <c r="G62" t="n">
         <v>20</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2374,6 +2684,11 @@
       <c r="G63" t="n">
         <v>15</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2405,6 +2720,11 @@
       <c r="G64" t="n">
         <v>12.5</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2436,6 +2756,11 @@
       <c r="G65" t="n">
         <v>10</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2467,6 +2792,11 @@
       <c r="G66" t="n">
         <v>7.5</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2498,6 +2828,11 @@
       <c r="G67" t="n">
         <v>5</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2529,6 +2864,11 @@
       <c r="G68" t="n">
         <v>50</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2560,6 +2900,11 @@
       <c r="G69" t="n">
         <v>25</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2591,6 +2936,11 @@
       <c r="G70" t="n">
         <v>20</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2622,6 +2972,11 @@
       <c r="G71" t="n">
         <v>5</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2653,6 +3008,11 @@
       <c r="G72" t="n">
         <v>75</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2684,6 +3044,11 @@
       <c r="G73" t="n">
         <v>15</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2715,6 +3080,11 @@
       <c r="G74" t="n">
         <v>5</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2746,6 +3116,11 @@
       <c r="G75" t="n">
         <v>5</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2777,6 +3152,11 @@
       <c r="G76" t="n">
         <v>32.43</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2808,6 +3188,11 @@
       <c r="G77" t="n">
         <v>24.32</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2839,6 +3224,11 @@
       <c r="G78" t="n">
         <v>16.22</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2870,6 +3260,11 @@
       <c r="G79" t="n">
         <v>10.81</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2901,6 +3296,11 @@
       <c r="G80" t="n">
         <v>8.109999999999999</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2932,6 +3332,11 @@
       <c r="G81" t="n">
         <v>8.109999999999999</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2963,6 +3368,11 @@
       <c r="G82" t="n">
         <v>50</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2994,6 +3404,11 @@
       <c r="G83" t="n">
         <v>35</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3025,6 +3440,11 @@
       <c r="G84" t="n">
         <v>10</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3056,6 +3476,11 @@
       <c r="G85" t="n">
         <v>5</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3087,6 +3512,11 @@
       <c r="G86" t="n">
         <v>70</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3118,6 +3548,11 @@
       <c r="G87" t="n">
         <v>15</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3149,6 +3584,11 @@
       <c r="G88" t="n">
         <v>10</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3180,6 +3620,11 @@
       <c r="G89" t="n">
         <v>5</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3211,6 +3656,11 @@
       <c r="G90" t="n">
         <v>31.37</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3242,6 +3692,11 @@
       <c r="G91" t="n">
         <v>25.49</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3273,6 +3728,11 @@
       <c r="G92" t="n">
         <v>23.53</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3304,6 +3764,11 @@
       <c r="G93" t="n">
         <v>7.84</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3335,6 +3800,11 @@
       <c r="G94" t="n">
         <v>7.84</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3366,6 +3836,11 @@
       <c r="G95" t="n">
         <v>3.92</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3397,6 +3872,11 @@
       <c r="G96" t="n">
         <v>75</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3428,6 +3908,11 @@
       <c r="G97" t="n">
         <v>25</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3459,6 +3944,11 @@
       <c r="G98" t="n">
         <v>50</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3490,6 +3980,11 @@
       <c r="G99" t="n">
         <v>25</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3521,6 +4016,11 @@
       <c r="G100" t="n">
         <v>20</v>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3552,6 +4052,11 @@
       <c r="G101" t="n">
         <v>5</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3583,6 +4088,11 @@
       <c r="G102" t="n">
         <v>29.03</v>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3614,6 +4124,11 @@
       <c r="G103" t="n">
         <v>25.81</v>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3645,6 +4160,11 @@
       <c r="G104" t="n">
         <v>16.13</v>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3676,6 +4196,11 @@
       <c r="G105" t="n">
         <v>12.9</v>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3707,6 +4232,11 @@
       <c r="G106" t="n">
         <v>6.45</v>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3738,6 +4268,11 @@
       <c r="G107" t="n">
         <v>6.45</v>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3769,6 +4304,11 @@
       <c r="G108" t="n">
         <v>3.23</v>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3800,6 +4340,11 @@
       <c r="G109" t="n">
         <v>50</v>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3831,6 +4376,11 @@
       <c r="G110" t="n">
         <v>40</v>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3862,6 +4412,11 @@
       <c r="G111" t="n">
         <v>9</v>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3893,6 +4448,11 @@
       <c r="G112" t="n">
         <v>1</v>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3924,6 +4484,11 @@
       <c r="G113" t="n">
         <v>60</v>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3955,6 +4520,11 @@
       <c r="G114" t="n">
         <v>25</v>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3986,6 +4556,11 @@
       <c r="G115" t="n">
         <v>10</v>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4017,6 +4592,11 @@
       <c r="G116" t="n">
         <v>5</v>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4048,6 +4628,11 @@
       <c r="G117" t="n">
         <v>38.1</v>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4079,6 +4664,11 @@
       <c r="G118" t="n">
         <v>20.63</v>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4110,6 +4700,11 @@
       <c r="G119" t="n">
         <v>19.05</v>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4141,6 +4736,11 @@
       <c r="G120" t="n">
         <v>12.7</v>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4172,6 +4772,11 @@
       <c r="G121" t="n">
         <v>6.35</v>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4203,6 +4808,11 @@
       <c r="G122" t="n">
         <v>3.17</v>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4234,6 +4844,11 @@
       <c r="G123" t="n">
         <v>80</v>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4265,6 +4880,11 @@
       <c r="G124" t="n">
         <v>20</v>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4296,6 +4916,11 @@
       <c r="G125" t="n">
         <v>17.67</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4327,6 +4952,11 @@
       <c r="G126" t="n">
         <v>16.28</v>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4358,6 +4988,11 @@
       <c r="G127" t="n">
         <v>13.95</v>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4389,6 +5024,11 @@
       <c r="G128" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4420,6 +5060,11 @@
       <c r="G129" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4451,6 +5096,11 @@
       <c r="G130" t="n">
         <v>6.98</v>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4482,6 +5132,11 @@
       <c r="G131" t="n">
         <v>6.98</v>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4513,6 +5168,11 @@
       <c r="G132" t="n">
         <v>6.98</v>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4544,6 +5204,11 @@
       <c r="G133" t="n">
         <v>4.65</v>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4575,6 +5240,11 @@
       <c r="G134" t="n">
         <v>4.19</v>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4606,6 +5276,11 @@
       <c r="G135" t="n">
         <v>2.33</v>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4637,6 +5312,11 @@
       <c r="G136" t="n">
         <v>0.93</v>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4668,6 +5348,11 @@
       <c r="G137" t="n">
         <v>0.47</v>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4699,6 +5384,11 @@
       <c r="G138" t="n">
         <v>32.5</v>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4730,6 +5420,11 @@
       <c r="G139" t="n">
         <v>16.25</v>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4761,6 +5456,11 @@
       <c r="G140" t="n">
         <v>16.25</v>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4792,6 +5492,11 @@
       <c r="G141" t="n">
         <v>12.5</v>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4823,6 +5528,11 @@
       <c r="G142" t="n">
         <v>12.5</v>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4854,6 +5564,11 @@
       <c r="G143" t="n">
         <v>10</v>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4885,6 +5600,11 @@
       <c r="G144" t="n">
         <v>100</v>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4916,6 +5636,11 @@
       <c r="G145" t="n">
         <v>70</v>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4947,6 +5672,11 @@
       <c r="G146" t="n">
         <v>20</v>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4978,6 +5708,11 @@
       <c r="G147" t="n">
         <v>10</v>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5009,6 +5744,11 @@
       <c r="G148" t="n">
         <v>19.32</v>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5040,6 +5780,11 @@
       <c r="G149" t="n">
         <v>18.68</v>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5071,6 +5816,11 @@
       <c r="G150" t="n">
         <v>16.1</v>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5102,6 +5852,11 @@
       <c r="G151" t="n">
         <v>12.88</v>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5133,6 +5888,11 @@
       <c r="G152" t="n">
         <v>12.88</v>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5164,6 +5924,11 @@
       <c r="G153" t="n">
         <v>6.44</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5195,6 +5960,11 @@
       <c r="G154" t="n">
         <v>3.38</v>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5226,6 +5996,11 @@
       <c r="G155" t="n">
         <v>3.22</v>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5257,6 +6032,11 @@
       <c r="G156" t="n">
         <v>2.58</v>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5288,6 +6068,11 @@
       <c r="G157" t="n">
         <v>1.93</v>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5319,6 +6104,11 @@
       <c r="G158" t="n">
         <v>1.93</v>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5350,6 +6140,11 @@
       <c r="G159" t="n">
         <v>0.64</v>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5381,6 +6176,11 @@
       <c r="G160" t="n">
         <v>100</v>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5412,6 +6212,11 @@
       <c r="G161" t="n">
         <v>70</v>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5443,6 +6248,11 @@
       <c r="G162" t="n">
         <v>20</v>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5474,6 +6284,11 @@
       <c r="G163" t="n">
         <v>10</v>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5505,6 +6320,11 @@
       <c r="G164" t="n">
         <v>15.73</v>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5536,6 +6356,11 @@
       <c r="G165" t="n">
         <v>11.69</v>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5567,6 +6392,11 @@
       <c r="G166" t="n">
         <v>9.890000000000001</v>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5598,6 +6428,11 @@
       <c r="G167" t="n">
         <v>9.890000000000001</v>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5629,6 +6464,11 @@
       <c r="G168" t="n">
         <v>8.99</v>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5660,6 +6500,11 @@
       <c r="G169" t="n">
         <v>8.99</v>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5691,6 +6536,11 @@
       <c r="G170" t="n">
         <v>8.99</v>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5722,6 +6572,11 @@
       <c r="G171" t="n">
         <v>7.87</v>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5753,6 +6608,11 @@
       <c r="G172" t="n">
         <v>4.49</v>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5784,6 +6644,11 @@
       <c r="G173" t="n">
         <v>4.49</v>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -5815,6 +6680,11 @@
       <c r="G174" t="n">
         <v>2.25</v>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -5846,6 +6716,11 @@
       <c r="G175" t="n">
         <v>2.25</v>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5877,6 +6752,11 @@
       <c r="G176" t="n">
         <v>2.25</v>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5908,6 +6788,11 @@
       <c r="G177" t="n">
         <v>2.25</v>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5939,6 +6824,11 @@
       <c r="G178" t="n">
         <v>50</v>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5970,6 +6860,11 @@
       <c r="G179" t="n">
         <v>20</v>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6001,6 +6896,11 @@
       <c r="G180" t="n">
         <v>15</v>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6032,6 +6932,11 @@
       <c r="G181" t="n">
         <v>10</v>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6063,6 +6968,11 @@
       <c r="G182" t="n">
         <v>5</v>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6094,6 +7004,11 @@
       <c r="G183" t="n">
         <v>55</v>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6125,6 +7040,11 @@
       <c r="G184" t="n">
         <v>30</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6156,6 +7076,11 @@
       <c r="G185" t="n">
         <v>15</v>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6187,6 +7112,11 @@
       <c r="G186" t="n">
         <v>19.15</v>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6218,6 +7148,11 @@
       <c r="G187" t="n">
         <v>14.89</v>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6249,6 +7184,11 @@
       <c r="G188" t="n">
         <v>12.77</v>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6280,6 +7220,11 @@
       <c r="G189" t="n">
         <v>12.77</v>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6311,6 +7256,11 @@
       <c r="G190" t="n">
         <v>12.77</v>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6342,6 +7292,11 @@
       <c r="G191" t="n">
         <v>10.64</v>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -6373,6 +7328,11 @@
       <c r="G192" t="n">
         <v>6.38</v>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -6404,6 +7364,11 @@
       <c r="G193" t="n">
         <v>6.38</v>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -6435,6 +7400,11 @@
       <c r="G194" t="n">
         <v>4.26</v>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -6466,6 +7436,11 @@
       <c r="G195" t="n">
         <v>50</v>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -6497,6 +7472,11 @@
       <c r="G196" t="n">
         <v>40</v>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -6528,6 +7508,11 @@
       <c r="G197" t="n">
         <v>10</v>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -6559,6 +7544,11 @@
       <c r="G198" t="n">
         <v>15.46</v>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -6590,6 +7580,11 @@
       <c r="G199" t="n">
         <v>14.43</v>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -6621,6 +7616,11 @@
       <c r="G200" t="n">
         <v>14.43</v>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -6652,6 +7652,11 @@
       <c r="G201" t="n">
         <v>12.37</v>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -6683,6 +7688,11 @@
       <c r="G202" t="n">
         <v>12.37</v>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -6714,6 +7724,11 @@
       <c r="G203" t="n">
         <v>8.25</v>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -6745,6 +7760,11 @@
       <c r="G204" t="n">
         <v>6.19</v>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -6776,6 +7796,11 @@
       <c r="G205" t="n">
         <v>4.12</v>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -6807,6 +7832,11 @@
       <c r="G206" t="n">
         <v>4.12</v>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -6838,6 +7868,11 @@
       <c r="G207" t="n">
         <v>2.06</v>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -6869,6 +7904,11 @@
       <c r="G208" t="n">
         <v>2.06</v>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -6900,6 +7940,11 @@
       <c r="G209" t="n">
         <v>2.06</v>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -6931,6 +7976,11 @@
       <c r="G210" t="n">
         <v>2.06</v>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -6962,6 +8012,11 @@
       <c r="G211" t="n">
         <v>50</v>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -6993,6 +8048,11 @@
       <c r="G212" t="n">
         <v>50</v>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -7024,6 +8084,11 @@
       <c r="G213" t="n">
         <v>58</v>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7055,6 +8120,11 @@
       <c r="G214" t="n">
         <v>40</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -7086,6 +8156,11 @@
       <c r="G215" t="n">
         <v>2</v>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7117,6 +8192,11 @@
       <c r="G216" t="n">
         <v>60</v>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -7148,6 +8228,11 @@
       <c r="G217" t="n">
         <v>25</v>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -7179,6 +8264,11 @@
       <c r="G218" t="n">
         <v>10</v>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -7210,6 +8300,11 @@
       <c r="G219" t="n">
         <v>5</v>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7241,6 +8336,11 @@
       <c r="G220" t="n">
         <v>31.58</v>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7272,6 +8372,11 @@
       <c r="G221" t="n">
         <v>21.05</v>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7303,6 +8408,11 @@
       <c r="G222" t="n">
         <v>15.79</v>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -7334,6 +8444,11 @@
       <c r="G223" t="n">
         <v>13.16</v>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -7365,6 +8480,11 @@
       <c r="G224" t="n">
         <v>10.53</v>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -7396,6 +8516,11 @@
       <c r="G225" t="n">
         <v>5.26</v>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -7427,6 +8552,11 @@
       <c r="G226" t="n">
         <v>2.63</v>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -7458,6 +8588,11 @@
       <c r="G227" t="n">
         <v>50</v>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -7489,6 +8624,11 @@
       <c r="G228" t="n">
         <v>35</v>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7520,6 +8660,11 @@
       <c r="G229" t="n">
         <v>15</v>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -7551,6 +8696,11 @@
       <c r="G230" t="n">
         <v>50</v>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -7582,6 +8732,11 @@
       <c r="G231" t="n">
         <v>35</v>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -7613,6 +8768,11 @@
       <c r="G232" t="n">
         <v>10</v>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -7644,6 +8804,11 @@
       <c r="G233" t="n">
         <v>5</v>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -7675,6 +8840,11 @@
       <c r="G234" t="n">
         <v>65</v>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -7706,6 +8876,11 @@
       <c r="G235" t="n">
         <v>20</v>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -7737,6 +8912,11 @@
       <c r="G236" t="n">
         <v>10</v>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -7768,6 +8948,11 @@
       <c r="G237" t="n">
         <v>5</v>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -7799,6 +8984,11 @@
       <c r="G238" t="n">
         <v>25.88</v>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -7830,6 +9020,11 @@
       <c r="G239" t="n">
         <v>17.65</v>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -7861,6 +9056,11 @@
       <c r="G240" t="n">
         <v>14.12</v>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -7892,6 +9092,11 @@
       <c r="G241" t="n">
         <v>14.12</v>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -7923,6 +9128,11 @@
       <c r="G242" t="n">
         <v>10.59</v>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -7954,6 +9164,11 @@
       <c r="G243" t="n">
         <v>7.06</v>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -7985,6 +9200,11 @@
       <c r="G244" t="n">
         <v>7.06</v>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8016,6 +9236,11 @@
       <c r="G245" t="n">
         <v>3.53</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -8047,6 +9272,11 @@
       <c r="G246" t="n">
         <v>75</v>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -8078,6 +9308,11 @@
       <c r="G247" t="n">
         <v>25</v>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -8109,6 +9344,11 @@
       <c r="G248" t="n">
         <v>30</v>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -8140,6 +9380,11 @@
       <c r="G249" t="n">
         <v>30</v>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -8171,6 +9416,11 @@
       <c r="G250" t="n">
         <v>25</v>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -8202,6 +9452,11 @@
       <c r="G251" t="n">
         <v>10</v>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -8233,6 +9488,11 @@
       <c r="G252" t="n">
         <v>5</v>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8264,6 +9524,11 @@
       <c r="G253" t="n">
         <v>55</v>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -8295,6 +9560,11 @@
       <c r="G254" t="n">
         <v>20</v>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -8326,6 +9596,11 @@
       <c r="G255" t="n">
         <v>15</v>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -8357,6 +9632,11 @@
       <c r="G256" t="n">
         <v>10</v>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -8388,6 +9668,11 @@
       <c r="G257" t="n">
         <v>24.14</v>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -8419,6 +9704,11 @@
       <c r="G258" t="n">
         <v>20.69</v>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8450,6 +9740,11 @@
       <c r="G259" t="n">
         <v>13.79</v>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -8481,6 +9776,11 @@
       <c r="G260" t="n">
         <v>6.9</v>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -8512,6 +9812,11 @@
       <c r="G261" t="n">
         <v>6.9</v>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -8543,6 +9848,11 @@
       <c r="G262" t="n">
         <v>6.9</v>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -8574,6 +9884,11 @@
       <c r="G263" t="n">
         <v>6.9</v>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -8605,6 +9920,11 @@
       <c r="G264" t="n">
         <v>6.9</v>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -8636,6 +9956,11 @@
       <c r="G265" t="n">
         <v>3.45</v>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -8667,6 +9992,11 @@
       <c r="G266" t="n">
         <v>3.45</v>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -8698,6 +10028,11 @@
       <c r="G267" t="n">
         <v>25.42</v>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -8729,6 +10064,11 @@
       <c r="G268" t="n">
         <v>20.34</v>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -8760,6 +10100,11 @@
       <c r="G269" t="n">
         <v>16.95</v>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -8791,6 +10136,11 @@
       <c r="G270" t="n">
         <v>6.78</v>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -8822,6 +10172,11 @@
       <c r="G271" t="n">
         <v>6.78</v>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -8853,6 +10208,11 @@
       <c r="G272" t="n">
         <v>6.78</v>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -8884,6 +10244,11 @@
       <c r="G273" t="n">
         <v>6.78</v>
       </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -8915,6 +10280,11 @@
       <c r="G274" t="n">
         <v>6.78</v>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -8946,6 +10316,11 @@
       <c r="G275" t="n">
         <v>3.39</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -8977,6 +10352,11 @@
       <c r="G276" t="n">
         <v>50</v>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -9008,6 +10388,11 @@
       <c r="G277" t="n">
         <v>35</v>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -9039,6 +10424,11 @@
       <c r="G278" t="n">
         <v>10</v>
       </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -9070,6 +10460,11 @@
       <c r="G279" t="n">
         <v>5</v>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -9101,6 +10496,11 @@
       <c r="G280" t="n">
         <v>21.28</v>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -9132,6 +10532,11 @@
       <c r="G281" t="n">
         <v>17.02</v>
       </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -9163,6 +10568,11 @@
       <c r="G282" t="n">
         <v>14.89</v>
       </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -9194,6 +10604,11 @@
       <c r="G283" t="n">
         <v>14.89</v>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -9225,6 +10640,11 @@
       <c r="G284" t="n">
         <v>12.77</v>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -9256,6 +10676,11 @@
       <c r="G285" t="n">
         <v>8.51</v>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -9287,6 +10712,11 @@
       <c r="G286" t="n">
         <v>6.38</v>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -9318,6 +10748,11 @@
       <c r="G287" t="n">
         <v>4.26</v>
       </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -9349,6 +10784,11 @@
       <c r="G288" t="n">
         <v>75</v>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -9380,6 +10820,11 @@
       <c r="G289" t="n">
         <v>25</v>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -9411,6 +10856,11 @@
       <c r="G290" t="n">
         <v>50</v>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -9442,6 +10892,11 @@
       <c r="G291" t="n">
         <v>35</v>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -9473,6 +10928,11 @@
       <c r="G292" t="n">
         <v>10</v>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -9504,6 +10964,11 @@
       <c r="G293" t="n">
         <v>5</v>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -9535,6 +11000,11 @@
       <c r="G294" t="n">
         <v>27.78</v>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -9566,6 +11036,11 @@
       <c r="G295" t="n">
         <v>19.44</v>
       </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -9597,6 +11072,11 @@
       <c r="G296" t="n">
         <v>16.67</v>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -9628,6 +11108,11 @@
       <c r="G297" t="n">
         <v>11.11</v>
       </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -9659,6 +11144,11 @@
       <c r="G298" t="n">
         <v>11.11</v>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -9690,6 +11180,11 @@
       <c r="G299" t="n">
         <v>5.56</v>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -9721,6 +11216,11 @@
       <c r="G300" t="n">
         <v>5.56</v>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -9752,6 +11252,11 @@
       <c r="G301" t="n">
         <v>2.78</v>
       </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -9783,6 +11288,11 @@
       <c r="G302" t="n">
         <v>75</v>
       </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -9814,6 +11324,11 @@
       <c r="G303" t="n">
         <v>25</v>
       </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -9845,6 +11360,11 @@
       <c r="G304" t="n">
         <v>25.85</v>
       </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -9876,6 +11396,11 @@
       <c r="G305" t="n">
         <v>23.91</v>
       </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -9907,6 +11432,11 @@
       <c r="G306" t="n">
         <v>16.16</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -9938,6 +11468,11 @@
       <c r="G307" t="n">
         <v>9.69</v>
       </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -9969,6 +11504,11 @@
       <c r="G308" t="n">
         <v>6.46</v>
       </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -10000,6 +11540,11 @@
       <c r="G309" t="n">
         <v>6.46</v>
       </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -10031,6 +11576,11 @@
       <c r="G310" t="n">
         <v>6.46</v>
       </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -10062,6 +11612,11 @@
       <c r="G311" t="n">
         <v>3.23</v>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -10093,6 +11648,11 @@
       <c r="G312" t="n">
         <v>1.78</v>
       </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -10124,6 +11684,11 @@
       <c r="G313" t="n">
         <v>75</v>
       </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -10155,6 +11720,11 @@
       <c r="G314" t="n">
         <v>25</v>
       </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -10186,6 +11756,11 @@
       <c r="G315" t="n">
         <v>50</v>
       </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -10217,6 +11792,11 @@
       <c r="G316" t="n">
         <v>35</v>
       </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -10248,6 +11828,11 @@
       <c r="G317" t="n">
         <v>10</v>
       </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -10279,6 +11864,11 @@
       <c r="G318" t="n">
         <v>5</v>
       </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -10310,6 +11900,11 @@
       <c r="G319" t="n">
         <v>20</v>
       </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -10341,6 +11936,11 @@
       <c r="G320" t="n">
         <v>20</v>
       </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -10372,6 +11972,11 @@
       <c r="G321" t="n">
         <v>17.5</v>
       </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -10403,6 +12008,11 @@
       <c r="G322" t="n">
         <v>15</v>
       </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -10434,6 +12044,11 @@
       <c r="G323" t="n">
         <v>10</v>
       </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -10465,6 +12080,11 @@
       <c r="G324" t="n">
         <v>5</v>
       </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -10496,6 +12116,11 @@
       <c r="G325" t="n">
         <v>5</v>
       </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -10527,6 +12152,11 @@
       <c r="G326" t="n">
         <v>5</v>
       </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -10558,6 +12188,11 @@
       <c r="G327" t="n">
         <v>2.5</v>
       </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -10589,6 +12224,11 @@
       <c r="G328" t="n">
         <v>70</v>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -10620,6 +12260,11 @@
       <c r="G329" t="n">
         <v>30</v>
       </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -10651,6 +12296,11 @@
       <c r="G330" t="n">
         <v>60</v>
       </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -10682,6 +12332,11 @@
       <c r="G331" t="n">
         <v>25</v>
       </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -10713,6 +12368,11 @@
       <c r="G332" t="n">
         <v>10</v>
       </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -10744,6 +12404,11 @@
       <c r="G333" t="n">
         <v>5</v>
       </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -10775,6 +12440,11 @@
       <c r="G334" t="n">
         <v>39.34</v>
       </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -10806,6 +12476,11 @@
       <c r="G335" t="n">
         <v>18.03</v>
       </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -10837,6 +12512,11 @@
       <c r="G336" t="n">
         <v>16.39</v>
       </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -10868,6 +12548,11 @@
       <c r="G337" t="n">
         <v>13.11</v>
       </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -10899,6 +12584,11 @@
       <c r="G338" t="n">
         <v>9.84</v>
       </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -10930,6 +12620,11 @@
       <c r="G339" t="n">
         <v>3.28</v>
       </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -10961,6 +12656,11 @@
       <c r="G340" t="n">
         <v>95</v>
       </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -10992,6 +12692,11 @@
       <c r="G341" t="n">
         <v>5</v>
       </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -11023,6 +12728,11 @@
       <c r="G342" t="n">
         <v>50</v>
       </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -11054,6 +12764,11 @@
       <c r="G343" t="n">
         <v>35</v>
       </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -11085,6 +12800,11 @@
       <c r="G344" t="n">
         <v>10</v>
       </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -11116,6 +12836,11 @@
       <c r="G345" t="n">
         <v>5</v>
       </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -11147,6 +12872,11 @@
       <c r="G346" t="n">
         <v>65</v>
       </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -11178,6 +12908,11 @@
       <c r="G347" t="n">
         <v>20</v>
       </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -11209,6 +12944,11 @@
       <c r="G348" t="n">
         <v>10</v>
       </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -11240,6 +12980,11 @@
       <c r="G349" t="n">
         <v>5</v>
       </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -11271,6 +13016,11 @@
       <c r="G350" t="n">
         <v>19.75</v>
       </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -11302,6 +13052,11 @@
       <c r="G351" t="n">
         <v>14.81</v>
       </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -11333,6 +13088,11 @@
       <c r="G352" t="n">
         <v>12.35</v>
       </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -11364,6 +13124,11 @@
       <c r="G353" t="n">
         <v>12.35</v>
       </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -11395,6 +13160,11 @@
       <c r="G354" t="n">
         <v>9.880000000000001</v>
       </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -11426,6 +13196,11 @@
       <c r="G355" t="n">
         <v>8.640000000000001</v>
       </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -11457,6 +13232,11 @@
       <c r="G356" t="n">
         <v>6.42</v>
       </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -11488,6 +13268,11 @@
       <c r="G357" t="n">
         <v>6.42</v>
       </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -11519,6 +13304,11 @@
       <c r="G358" t="n">
         <v>4.94</v>
       </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -11550,6 +13340,11 @@
       <c r="G359" t="n">
         <v>2.47</v>
       </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -11581,6 +13376,11 @@
       <c r="G360" t="n">
         <v>0.99</v>
       </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -11612,6 +13412,11 @@
       <c r="G361" t="n">
         <v>0.99</v>
       </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -11643,6 +13448,11 @@
       <c r="G362" t="n">
         <v>100</v>
       </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -11674,6 +13484,11 @@
       <c r="G363" t="n">
         <v>70</v>
       </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -11705,6 +13520,11 @@
       <c r="G364" t="n">
         <v>20</v>
       </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -11736,6 +13556,11 @@
       <c r="G365" t="n">
         <v>10</v>
       </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -11767,6 +13592,11 @@
       <c r="G366" t="n">
         <v>17.5</v>
       </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -11798,6 +13628,11 @@
       <c r="G367" t="n">
         <v>15</v>
       </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -11829,6 +13664,11 @@
       <c r="G368" t="n">
         <v>14.5</v>
       </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -11860,6 +13700,11 @@
       <c r="G369" t="n">
         <v>10</v>
       </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -11891,6 +13736,11 @@
       <c r="G370" t="n">
         <v>9</v>
       </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -11922,6 +13772,11 @@
       <c r="G371" t="n">
         <v>6.25</v>
       </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -11953,6 +13808,11 @@
       <c r="G372" t="n">
         <v>6.25</v>
       </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -11984,6 +13844,11 @@
       <c r="G373" t="n">
         <v>5</v>
       </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -12015,6 +13880,11 @@
       <c r="G374" t="n">
         <v>5</v>
       </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -12046,6 +13916,11 @@
       <c r="G375" t="n">
         <v>5</v>
       </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -12077,6 +13952,11 @@
       <c r="G376" t="n">
         <v>2.5</v>
       </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -12108,6 +13988,11 @@
       <c r="G377" t="n">
         <v>1.5</v>
       </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -12139,6 +14024,11 @@
       <c r="G378" t="n">
         <v>1.5</v>
       </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -12170,6 +14060,11 @@
       <c r="G379" t="n">
         <v>1</v>
       </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -12201,6 +14096,11 @@
       <c r="G380" t="n">
         <v>100</v>
       </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -12232,6 +14132,11 @@
       <c r="G381" t="n">
         <v>16</v>
       </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -12263,6 +14168,11 @@
       <c r="G382" t="n">
         <v>13.33</v>
       </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -12294,6 +14204,11 @@
       <c r="G383" t="n">
         <v>10.67</v>
       </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -12325,6 +14240,11 @@
       <c r="G384" t="n">
         <v>10.67</v>
       </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -12356,6 +14276,11 @@
       <c r="G385" t="n">
         <v>10.67</v>
       </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -12387,6 +14312,11 @@
       <c r="G386" t="n">
         <v>6.67</v>
       </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -12418,6 +14348,11 @@
       <c r="G387" t="n">
         <v>6.67</v>
       </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -12449,6 +14384,11 @@
       <c r="G388" t="n">
         <v>6.67</v>
       </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -12480,6 +14420,11 @@
       <c r="G389" t="n">
         <v>5.33</v>
       </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -12511,6 +14456,11 @@
       <c r="G390" t="n">
         <v>5.33</v>
       </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -12542,6 +14492,11 @@
       <c r="G391" t="n">
         <v>5.33</v>
       </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -12573,6 +14528,11 @@
       <c r="G392" t="n">
         <v>2.67</v>
       </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -12604,6 +14564,11 @@
       <c r="G393" t="n">
         <v>13.95</v>
       </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -12635,6 +14600,11 @@
       <c r="G394" t="n">
         <v>11.63</v>
       </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -12666,6 +14636,11 @@
       <c r="G395" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -12697,6 +14672,11 @@
       <c r="G396" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -12728,6 +14708,11 @@
       <c r="G397" t="n">
         <v>8.140000000000001</v>
       </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -12759,6 +14744,11 @@
       <c r="G398" t="n">
         <v>8.140000000000001</v>
       </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -12790,6 +14780,11 @@
       <c r="G399" t="n">
         <v>6.98</v>
       </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -12821,6 +14816,11 @@
       <c r="G400" t="n">
         <v>4.65</v>
       </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -12852,6 +14852,11 @@
       <c r="G401" t="n">
         <v>4.65</v>
       </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -12883,6 +14888,11 @@
       <c r="G402" t="n">
         <v>4.65</v>
       </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -12914,6 +14924,11 @@
       <c r="G403" t="n">
         <v>4.65</v>
       </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -12945,6 +14960,11 @@
       <c r="G404" t="n">
         <v>3.72</v>
       </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -12976,6 +14996,11 @@
       <c r="G405" t="n">
         <v>2.33</v>
       </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -13007,6 +15032,11 @@
       <c r="G406" t="n">
         <v>2.33</v>
       </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -13038,6 +15068,11 @@
       <c r="G407" t="n">
         <v>2.33</v>
       </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -13069,6 +15104,11 @@
       <c r="G408" t="n">
         <v>2.33</v>
       </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -13100,6 +15140,11 @@
       <c r="G409" t="n">
         <v>0.93</v>
       </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -13131,6 +15176,11 @@
       <c r="G410" t="n">
         <v>60</v>
       </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -13162,6 +15212,11 @@
       <c r="G411" t="n">
         <v>30</v>
       </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -13193,6 +15248,11 @@
       <c r="G412" t="n">
         <v>10</v>
       </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -13224,6 +15284,11 @@
       <c r="G413" t="n">
         <v>40</v>
       </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -13255,6 +15320,11 @@
       <c r="G414" t="n">
         <v>30</v>
       </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -13286,6 +15356,11 @@
       <c r="G415" t="n">
         <v>25</v>
       </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -13317,6 +15392,11 @@
       <c r="G416" t="n">
         <v>5</v>
       </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -13348,6 +15428,11 @@
       <c r="G417" t="n">
         <v>20</v>
       </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -13379,6 +15464,11 @@
       <c r="G418" t="n">
         <v>20</v>
       </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -13410,6 +15500,11 @@
       <c r="G419" t="n">
         <v>15</v>
       </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -13441,6 +15536,11 @@
       <c r="G420" t="n">
         <v>12.5</v>
       </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -13472,6 +15572,11 @@
       <c r="G421" t="n">
         <v>10</v>
       </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -13503,6 +15608,11 @@
       <c r="G422" t="n">
         <v>10</v>
       </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -13534,6 +15644,11 @@
       <c r="G423" t="n">
         <v>7.5</v>
       </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -13565,6 +15680,11 @@
       <c r="G424" t="n">
         <v>2.5</v>
       </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -13596,6 +15716,11 @@
       <c r="G425" t="n">
         <v>2.5</v>
       </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -13627,6 +15752,11 @@
       <c r="G426" t="n">
         <v>16.15</v>
       </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -13658,6 +15788,11 @@
       <c r="G427" t="n">
         <v>14.8</v>
       </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -13689,6 +15824,11 @@
       <c r="G428" t="n">
         <v>12.11</v>
       </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -13720,6 +15860,11 @@
       <c r="G429" t="n">
         <v>8.08</v>
       </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -13751,6 +15896,11 @@
       <c r="G430" t="n">
         <v>8.08</v>
       </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -13782,6 +15932,11 @@
       <c r="G431" t="n">
         <v>8.08</v>
       </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -13813,6 +15968,11 @@
       <c r="G432" t="n">
         <v>8.08</v>
       </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -13844,6 +16004,11 @@
       <c r="G433" t="n">
         <v>8.08</v>
       </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -13875,6 +16040,11 @@
       <c r="G434" t="n">
         <v>7.27</v>
       </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -13906,6 +16076,11 @@
       <c r="G435" t="n">
         <v>5.25</v>
       </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -13937,6 +16112,11 @@
       <c r="G436" t="n">
         <v>4.04</v>
       </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -13968,6 +16148,11 @@
       <c r="G437" t="n">
         <v>19.8</v>
       </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -13999,6 +16184,11 @@
       <c r="G438" t="n">
         <v>14.85</v>
       </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -14030,6 +16220,11 @@
       <c r="G439" t="n">
         <v>14.85</v>
       </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -14061,6 +16256,11 @@
       <c r="G440" t="n">
         <v>13.86</v>
       </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -14092,6 +16292,11 @@
       <c r="G441" t="n">
         <v>12.38</v>
       </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -14123,6 +16328,11 @@
       <c r="G442" t="n">
         <v>7.43</v>
       </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -14154,6 +16364,11 @@
       <c r="G443" t="n">
         <v>6.93</v>
       </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -14185,6 +16400,11 @@
       <c r="G444" t="n">
         <v>4.95</v>
       </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -14216,6 +16436,11 @@
       <c r="G445" t="n">
         <v>2.48</v>
       </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -14247,6 +16472,11 @@
       <c r="G446" t="n">
         <v>0.99</v>
       </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -14278,6 +16508,11 @@
       <c r="G447" t="n">
         <v>0.99</v>
       </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -14309,6 +16544,11 @@
       <c r="G448" t="n">
         <v>0.5</v>
       </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -14340,6 +16580,11 @@
       <c r="G449" t="n">
         <v>70</v>
       </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -14371,6 +16616,11 @@
       <c r="G450" t="n">
         <v>30</v>
       </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -14402,6 +16652,11 @@
       <c r="G451" t="n">
         <v>50</v>
       </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -14433,6 +16688,11 @@
       <c r="G452" t="n">
         <v>40</v>
       </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -14464,6 +16724,11 @@
       <c r="G453" t="n">
         <v>10</v>
       </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -14495,6 +16760,11 @@
       <c r="G454" t="n">
         <v>35</v>
       </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -14526,6 +16796,11 @@
       <c r="G455" t="n">
         <v>35</v>
       </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -14557,6 +16832,11 @@
       <c r="G456" t="n">
         <v>30</v>
       </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -14588,6 +16868,11 @@
       <c r="G457" t="n">
         <v>34.13</v>
       </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -14619,6 +16904,11 @@
       <c r="G458" t="n">
         <v>24.6</v>
       </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -14650,6 +16940,11 @@
       <c r="G459" t="n">
         <v>23.81</v>
       </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -14681,6 +16976,11 @@
       <c r="G460" t="n">
         <v>7.94</v>
       </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -14712,6 +17012,11 @@
       <c r="G461" t="n">
         <v>3.97</v>
       </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -14743,6 +17048,11 @@
       <c r="G462" t="n">
         <v>3.97</v>
       </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -14774,6 +17084,11 @@
       <c r="G463" t="n">
         <v>1.59</v>
       </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -14805,6 +17120,11 @@
       <c r="G464" t="n">
         <v>70</v>
       </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -14836,6 +17156,11 @@
       <c r="G465" t="n">
         <v>30</v>
       </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -14867,6 +17192,11 @@
       <c r="G466" t="n">
         <v>50</v>
       </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -14898,6 +17228,11 @@
       <c r="G467" t="n">
         <v>40</v>
       </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -14929,6 +17264,11 @@
       <c r="G468" t="n">
         <v>10</v>
       </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -14960,6 +17300,11 @@
       <c r="G469" t="n">
         <v>32.09</v>
       </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -14991,6 +17336,11 @@
       <c r="G470" t="n">
         <v>22.39</v>
       </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -15022,6 +17372,11 @@
       <c r="G471" t="n">
         <v>17.16</v>
       </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -15053,6 +17408,11 @@
       <c r="G472" t="n">
         <v>11.94</v>
       </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -15084,6 +17444,11 @@
       <c r="G473" t="n">
         <v>7.46</v>
       </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -15115,6 +17480,11 @@
       <c r="G474" t="n">
         <v>3.73</v>
       </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -15146,6 +17516,11 @@
       <c r="G475" t="n">
         <v>3.73</v>
       </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -15177,6 +17552,11 @@
       <c r="G476" t="n">
         <v>1.49</v>
       </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -15208,6 +17588,11 @@
       <c r="G477" t="n">
         <v>50</v>
       </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -15239,6 +17624,11 @@
       <c r="G478" t="n">
         <v>50</v>
       </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -15270,6 +17660,11 @@
       <c r="G479" t="n">
         <v>56</v>
       </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -15301,6 +17696,11 @@
       <c r="G480" t="n">
         <v>16</v>
       </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -15332,6 +17732,11 @@
       <c r="G481" t="n">
         <v>16</v>
       </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -15363,6 +17768,11 @@
       <c r="G482" t="n">
         <v>5</v>
       </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -15394,6 +17804,11 @@
       <c r="G483" t="n">
         <v>5</v>
       </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -15425,6 +17840,11 @@
       <c r="G484" t="n">
         <v>2</v>
       </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -15456,6 +17876,11 @@
       <c r="G485" t="n">
         <v>70</v>
       </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -15487,6 +17912,11 @@
       <c r="G486" t="n">
         <v>30</v>
       </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -15518,6 +17948,11 @@
       <c r="G487" t="n">
         <v>50</v>
       </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -15549,6 +17984,11 @@
       <c r="G488" t="n">
         <v>40</v>
       </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -15580,6 +18020,11 @@
       <c r="G489" t="n">
         <v>10</v>
       </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -15611,6 +18056,11 @@
       <c r="G490" t="n">
         <v>28</v>
       </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -15642,6 +18092,11 @@
       <c r="G491" t="n">
         <v>16</v>
       </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -15673,6 +18128,11 @@
       <c r="G492" t="n">
         <v>15</v>
       </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -15704,6 +18164,11 @@
       <c r="G493" t="n">
         <v>15</v>
       </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -15735,6 +18200,11 @@
       <c r="G494" t="n">
         <v>15</v>
       </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -15766,6 +18236,11 @@
       <c r="G495" t="n">
         <v>5</v>
       </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -15797,6 +18272,11 @@
       <c r="G496" t="n">
         <v>2.5</v>
       </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -15828,6 +18308,11 @@
       <c r="G497" t="n">
         <v>2.5</v>
       </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -15859,6 +18344,11 @@
       <c r="G498" t="n">
         <v>1</v>
       </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -15890,6 +18380,11 @@
       <c r="G499" t="n">
         <v>34.8</v>
       </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -15921,6 +18416,11 @@
       <c r="G500" t="n">
         <v>22.06</v>
       </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -15952,6 +18452,11 @@
       <c r="G501" t="n">
         <v>15.2</v>
       </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -15983,6 +18488,11 @@
       <c r="G502" t="n">
         <v>11.76</v>
       </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -16014,6 +18524,11 @@
       <c r="G503" t="n">
         <v>7.35</v>
       </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -16045,6 +18560,11 @@
       <c r="G504" t="n">
         <v>3.68</v>
       </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -16076,6 +18596,11 @@
       <c r="G505" t="n">
         <v>3.68</v>
       </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -16107,6 +18632,11 @@
       <c r="G506" t="n">
         <v>1.47</v>
       </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -16138,6 +18668,11 @@
       <c r="G507" t="n">
         <v>50</v>
       </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -16169,6 +18704,11 @@
       <c r="G508" t="n">
         <v>40</v>
       </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -16200,6 +18740,11 @@
       <c r="G509" t="n">
         <v>10</v>
       </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -16231,6 +18776,11 @@
       <c r="G510" t="n">
         <v>60</v>
       </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -16262,6 +18812,11 @@
       <c r="G511" t="n">
         <v>40</v>
       </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -16293,6 +18848,11 @@
       <c r="G512" t="n">
         <v>63.93</v>
       </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -16324,6 +18884,11 @@
       <c r="G513" t="n">
         <v>13.11</v>
       </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -16355,6 +18920,11 @@
       <c r="G514" t="n">
         <v>13.11</v>
       </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -16386,6 +18956,11 @@
       <c r="G515" t="n">
         <v>4.1</v>
       </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -16417,6 +18992,11 @@
       <c r="G516" t="n">
         <v>4.1</v>
       </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -16448,6 +19028,11 @@
       <c r="G517" t="n">
         <v>1.64</v>
       </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -16479,6 +19064,11 @@
       <c r="G518" t="n">
         <v>70</v>
       </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -16510,6 +19100,11 @@
       <c r="G519" t="n">
         <v>30</v>
       </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -16541,6 +19136,11 @@
       <c r="G520" t="n">
         <v>50</v>
       </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -16572,6 +19172,11 @@
       <c r="G521" t="n">
         <v>40</v>
       </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -16603,6 +19208,11 @@
       <c r="G522" t="n">
         <v>10</v>
       </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -16634,6 +19244,11 @@
       <c r="G523" t="n">
         <v>45</v>
       </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -16665,6 +19280,11 @@
       <c r="G524" t="n">
         <v>30</v>
       </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -16696,6 +19316,11 @@
       <c r="G525" t="n">
         <v>25</v>
       </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -16727,6 +19352,11 @@
       <c r="G526" t="n">
         <v>32.09</v>
       </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -16758,6 +19388,11 @@
       <c r="G527" t="n">
         <v>22.39</v>
       </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -16789,6 +19424,11 @@
       <c r="G528" t="n">
         <v>17.16</v>
       </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -16820,6 +19460,11 @@
       <c r="G529" t="n">
         <v>11.94</v>
       </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -16851,6 +19496,11 @@
       <c r="G530" t="n">
         <v>7.46</v>
       </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -16882,6 +19532,11 @@
       <c r="G531" t="n">
         <v>3.73</v>
       </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -16913,6 +19568,11 @@
       <c r="G532" t="n">
         <v>3.73</v>
       </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -16944,6 +19604,11 @@
       <c r="G533" t="n">
         <v>1.49</v>
       </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -16975,6 +19640,11 @@
       <c r="G534" t="n">
         <v>70</v>
       </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -17006,6 +19676,11 @@
       <c r="G535" t="n">
         <v>30</v>
       </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -17037,6 +19712,11 @@
       <c r="G536" t="n">
         <v>50</v>
       </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -17068,6 +19748,11 @@
       <c r="G537" t="n">
         <v>40</v>
       </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -17099,6 +19784,11 @@
       <c r="G538" t="n">
         <v>10</v>
       </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -17130,6 +19820,11 @@
       <c r="G539" t="n">
         <v>45</v>
       </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -17161,6 +19856,11 @@
       <c r="G540" t="n">
         <v>45</v>
       </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -17192,6 +19892,11 @@
       <c r="G541" t="n">
         <v>10</v>
       </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -17223,6 +19928,11 @@
       <c r="G542" t="n">
         <v>39.18</v>
       </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -17254,6 +19964,11 @@
       <c r="G543" t="n">
         <v>20.5</v>
       </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -17285,6 +20000,11 @@
       <c r="G544" t="n">
         <v>10.93</v>
       </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -17316,6 +20036,11 @@
       <c r="G545" t="n">
         <v>10.93</v>
       </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -17347,6 +20072,11 @@
       <c r="G546" t="n">
         <v>6.83</v>
       </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -17378,6 +20108,11 @@
       <c r="G547" t="n">
         <v>3.42</v>
       </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -17409,6 +20144,11 @@
       <c r="G548" t="n">
         <v>3.42</v>
       </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -17440,6 +20180,11 @@
       <c r="G549" t="n">
         <v>3.42</v>
       </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -17471,6 +20216,11 @@
       <c r="G550" t="n">
         <v>1.37</v>
       </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -17502,6 +20252,11 @@
       <c r="G551" t="n">
         <v>56</v>
       </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -17533,6 +20288,11 @@
       <c r="G552" t="n">
         <v>32</v>
       </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -17564,6 +20324,11 @@
       <c r="G553" t="n">
         <v>5</v>
       </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -17595,6 +20360,11 @@
       <c r="G554" t="n">
         <v>5</v>
       </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -17626,6 +20396,11 @@
       <c r="G555" t="n">
         <v>2</v>
       </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -17657,6 +20432,11 @@
       <c r="G556" t="n">
         <v>53.33</v>
       </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -17688,6 +20468,11 @@
       <c r="G557" t="n">
         <v>30.48</v>
       </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -17719,6 +20504,11 @@
       <c r="G558" t="n">
         <v>4.76</v>
       </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -17750,6 +20540,11 @@
       <c r="G559" t="n">
         <v>4.76</v>
       </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -17781,6 +20576,11 @@
       <c r="G560" t="n">
         <v>4.76</v>
       </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -17812,6 +20612,11 @@
       <c r="G561" t="n">
         <v>1.9</v>
       </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -17843,6 +20648,11 @@
       <c r="G562" t="n">
         <v>70</v>
       </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -17874,6 +20684,11 @@
       <c r="G563" t="n">
         <v>30</v>
       </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -17905,6 +20720,11 @@
       <c r="G564" t="n">
         <v>50</v>
       </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -17936,6 +20756,11 @@
       <c r="G565" t="n">
         <v>40</v>
       </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -17967,6 +20792,11 @@
       <c r="G566" t="n">
         <v>10</v>
       </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -17998,6 +20828,11 @@
       <c r="G567" t="n">
         <v>33.02</v>
       </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -18029,6 +20864,11 @@
       <c r="G568" t="n">
         <v>28.3</v>
       </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -18060,6 +20900,11 @@
       <c r="G569" t="n">
         <v>26.42</v>
       </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -18091,6 +20936,11 @@
       <c r="G570" t="n">
         <v>4.72</v>
       </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -18122,6 +20972,11 @@
       <c r="G571" t="n">
         <v>4.72</v>
       </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -18153,6 +21008,11 @@
       <c r="G572" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -18184,6 +21044,11 @@
       <c r="G573" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -18215,6 +21080,11 @@
       <c r="G574" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -18246,6 +21116,11 @@
       <c r="G575" t="n">
         <v>46.28</v>
       </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -18277,6 +21152,11 @@
       <c r="G576" t="n">
         <v>24.79</v>
       </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -18308,6 +21188,11 @@
       <c r="G577" t="n">
         <v>19.01</v>
       </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -18339,6 +21224,11 @@
       <c r="G578" t="n">
         <v>8.26</v>
       </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -18370,6 +21260,11 @@
       <c r="G579" t="n">
         <v>1.65</v>
       </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -18401,6 +21296,11 @@
       <c r="G580" t="n">
         <v>54.55</v>
       </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -18432,6 +21332,11 @@
       <c r="G581" t="n">
         <v>27.27</v>
       </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -18463,6 +21368,11 @@
       <c r="G582" t="n">
         <v>9.09</v>
       </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -18494,6 +21404,11 @@
       <c r="G583" t="n">
         <v>9.09</v>
       </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -18525,6 +21440,11 @@
       <c r="G584" t="n">
         <v>60</v>
       </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -18556,6 +21476,11 @@
       <c r="G585" t="n">
         <v>40</v>
       </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -18587,6 +21512,11 @@
       <c r="G586" t="n">
         <v>28.3</v>
       </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -18618,6 +21548,11 @@
       <c r="G587" t="n">
         <v>26.42</v>
       </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -18649,6 +21584,11 @@
       <c r="G588" t="n">
         <v>18.87</v>
       </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -18680,6 +21620,11 @@
       <c r="G589" t="n">
         <v>14.15</v>
       </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -18711,6 +21656,11 @@
       <c r="G590" t="n">
         <v>4.72</v>
       </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -18742,6 +21692,11 @@
       <c r="G591" t="n">
         <v>4.72</v>
       </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -18773,6 +21728,11 @@
       <c r="G592" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -18804,6 +21764,11 @@
       <c r="G593" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -18835,6 +21800,11 @@
       <c r="G594" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -18866,6 +21836,11 @@
       <c r="G595" t="n">
         <v>46.33</v>
       </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -18897,6 +21872,11 @@
       <c r="G596" t="n">
         <v>16.95</v>
       </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -18928,6 +21908,11 @@
       <c r="G597" t="n">
         <v>16.95</v>
       </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -18959,6 +21944,11 @@
       <c r="G598" t="n">
         <v>12.99</v>
       </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -18990,6 +21980,11 @@
       <c r="G599" t="n">
         <v>5.65</v>
       </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -19021,6 +22016,11 @@
       <c r="G600" t="n">
         <v>1.13</v>
       </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -19052,6 +22052,11 @@
       <c r="G601" t="n">
         <v>70</v>
       </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -19083,6 +22088,11 @@
       <c r="G602" t="n">
         <v>30</v>
       </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -19114,6 +22124,11 @@
       <c r="G603" t="n">
         <v>60</v>
       </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -19145,6 +22160,11 @@
       <c r="G604" t="n">
         <v>40</v>
       </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -19176,6 +22196,11 @@
       <c r="G605" t="n">
         <v>28.3</v>
       </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -19207,6 +22232,11 @@
       <c r="G606" t="n">
         <v>26.42</v>
       </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -19238,6 +22268,11 @@
       <c r="G607" t="n">
         <v>18.87</v>
       </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -19269,6 +22304,11 @@
       <c r="G608" t="n">
         <v>14.15</v>
       </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -19300,6 +22340,11 @@
       <c r="G609" t="n">
         <v>4.72</v>
       </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -19331,6 +22376,11 @@
       <c r="G610" t="n">
         <v>4.72</v>
       </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -19362,6 +22412,11 @@
       <c r="G611" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -19393,6 +22448,11 @@
       <c r="G612" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -19424,6 +22484,11 @@
       <c r="G613" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -19455,6 +22520,11 @@
       <c r="G614" t="n">
         <v>30</v>
       </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -19486,6 +22556,11 @@
       <c r="G615" t="n">
         <v>30</v>
       </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -19517,6 +22592,11 @@
       <c r="G616" t="n">
         <v>30</v>
       </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -19548,6 +22628,11 @@
       <c r="G617" t="n">
         <v>10</v>
       </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -19579,6 +22664,11 @@
       <c r="G618" t="n">
         <v>60</v>
       </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -19610,6 +22700,11 @@
       <c r="G619" t="n">
         <v>40</v>
       </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -19641,6 +22736,11 @@
       <c r="G620" t="n">
         <v>28.3</v>
       </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -19672,6 +22772,11 @@
       <c r="G621" t="n">
         <v>26.42</v>
       </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -19703,6 +22808,11 @@
       <c r="G622" t="n">
         <v>18.87</v>
       </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -19734,6 +22844,11 @@
       <c r="G623" t="n">
         <v>14.15</v>
       </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -19765,6 +22880,11 @@
       <c r="G624" t="n">
         <v>4.72</v>
       </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -19796,6 +22916,11 @@
       <c r="G625" t="n">
         <v>4.72</v>
       </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -19827,6 +22952,11 @@
       <c r="G626" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -19858,6 +22988,11 @@
       <c r="G627" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -19889,6 +23024,11 @@
       <c r="G628" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -19920,6 +23060,11 @@
       <c r="G629" t="n">
         <v>50</v>
       </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -19951,6 +23096,11 @@
       <c r="G630" t="n">
         <v>50</v>
       </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -19982,6 +23132,11 @@
       <c r="G631" t="n">
         <v>60</v>
       </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -20013,6 +23168,11 @@
       <c r="G632" t="n">
         <v>40</v>
       </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -20044,6 +23204,11 @@
       <c r="G633" t="n">
         <v>28.3</v>
       </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -20075,6 +23240,11 @@
       <c r="G634" t="n">
         <v>26.42</v>
       </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -20106,6 +23276,11 @@
       <c r="G635" t="n">
         <v>18.87</v>
       </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -20137,6 +23312,11 @@
       <c r="G636" t="n">
         <v>14.15</v>
       </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -20168,6 +23348,11 @@
       <c r="G637" t="n">
         <v>4.72</v>
       </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -20199,6 +23384,11 @@
       <c r="G638" t="n">
         <v>4.72</v>
       </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -20230,6 +23420,11 @@
       <c r="G639" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -20261,6 +23456,11 @@
       <c r="G640" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -20292,6 +23492,11 @@
       <c r="G641" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -20323,6 +23528,11 @@
       <c r="G642" t="n">
         <v>46.28</v>
       </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -20354,6 +23564,11 @@
       <c r="G643" t="n">
         <v>24.79</v>
       </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -20385,6 +23600,11 @@
       <c r="G644" t="n">
         <v>19.01</v>
       </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -20416,6 +23636,11 @@
       <c r="G645" t="n">
         <v>8.26</v>
       </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -20447,6 +23672,11 @@
       <c r="G646" t="n">
         <v>1.65</v>
       </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -20478,6 +23708,11 @@
       <c r="G647" t="n">
         <v>60</v>
       </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -20509,6 +23744,11 @@
       <c r="G648" t="n">
         <v>30</v>
       </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -20540,6 +23780,11 @@
       <c r="G649" t="n">
         <v>10</v>
       </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -20571,6 +23816,11 @@
       <c r="G650" t="n">
         <v>40</v>
       </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -20602,6 +23852,11 @@
       <c r="G651" t="n">
         <v>40</v>
       </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -20633,6 +23888,11 @@
       <c r="G652" t="n">
         <v>20</v>
       </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -20664,6 +23924,11 @@
       <c r="G653" t="n">
         <v>45</v>
       </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -20695,6 +23960,11 @@
       <c r="G654" t="n">
         <v>45</v>
       </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -20726,6 +23996,11 @@
       <c r="G655" t="n">
         <v>10</v>
       </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -20757,6 +24032,11 @@
       <c r="G656" t="n">
         <v>30.94</v>
       </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -20788,6 +24068,11 @@
       <c r="G657" t="n">
         <v>21.58</v>
       </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -20819,6 +24104,11 @@
       <c r="G658" t="n">
         <v>16.55</v>
       </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -20850,6 +24140,11 @@
       <c r="G659" t="n">
         <v>11.51</v>
       </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -20881,6 +24176,11 @@
       <c r="G660" t="n">
         <v>7.19</v>
       </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -20912,6 +24212,11 @@
       <c r="G661" t="n">
         <v>3.6</v>
       </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -20943,6 +24248,11 @@
       <c r="G662" t="n">
         <v>3.6</v>
       </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -20974,6 +24284,11 @@
       <c r="G663" t="n">
         <v>3.6</v>
       </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -21005,6 +24320,11 @@
       <c r="G664" t="n">
         <v>1.44</v>
       </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -21036,6 +24356,11 @@
       <c r="G665" t="n">
         <v>70</v>
       </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -21067,6 +24392,11 @@
       <c r="G666" t="n">
         <v>30</v>
       </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -21098,6 +24428,11 @@
       <c r="G667" t="n">
         <v>16.81</v>
       </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -21129,6 +24464,11 @@
       <c r="G668" t="n">
         <v>15.94</v>
       </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -21160,6 +24500,11 @@
       <c r="G669" t="n">
         <v>14.49</v>
       </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -21191,6 +24536,11 @@
       <c r="G670" t="n">
         <v>14.49</v>
       </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -21222,6 +24572,11 @@
       <c r="G671" t="n">
         <v>14.49</v>
       </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -21253,6 +24608,11 @@
       <c r="G672" t="n">
         <v>11.59</v>
       </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -21284,6 +24644,11 @@
       <c r="G673" t="n">
         <v>5.8</v>
       </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -21315,6 +24680,11 @@
       <c r="G674" t="n">
         <v>5.8</v>
       </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -21346,6 +24716,11 @@
       <c r="G675" t="n">
         <v>0.58</v>
       </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -21377,6 +24752,11 @@
       <c r="G676" t="n">
         <v>70</v>
       </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -21408,6 +24788,11 @@
       <c r="G677" t="n">
         <v>30</v>
       </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -21439,6 +24824,11 @@
       <c r="G678" t="n">
         <v>19.5</v>
       </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -21470,6 +24860,11 @@
       <c r="G679" t="n">
         <v>12.5</v>
       </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -21501,6 +24896,11 @@
       <c r="G680" t="n">
         <v>12.5</v>
       </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -21532,6 +24932,11 @@
       <c r="G681" t="n">
         <v>12.5</v>
       </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -21563,6 +24968,11 @@
       <c r="G682" t="n">
         <v>12.5</v>
       </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -21594,6 +25004,11 @@
       <c r="G683" t="n">
         <v>10</v>
       </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -21625,6 +25040,11 @@
       <c r="G684" t="n">
         <v>10</v>
       </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -21656,6 +25076,11 @@
       <c r="G685" t="n">
         <v>5</v>
       </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -21687,6 +25112,11 @@
       <c r="G686" t="n">
         <v>5</v>
       </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -21718,6 +25148,11 @@
       <c r="G687" t="n">
         <v>0.5</v>
       </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -21749,6 +25184,11 @@
       <c r="G688" t="n">
         <v>80</v>
       </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -21780,6 +25220,11 @@
       <c r="G689" t="n">
         <v>20</v>
       </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -21811,6 +25256,11 @@
       <c r="G690" t="n">
         <v>20</v>
       </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -21842,6 +25292,11 @@
       <c r="G691" t="n">
         <v>20</v>
       </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -21873,6 +25328,11 @@
       <c r="G692" t="n">
         <v>20</v>
       </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -21904,6 +25364,11 @@
       <c r="G693" t="n">
         <v>15</v>
       </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -21935,6 +25400,11 @@
       <c r="G694" t="n">
         <v>15</v>
       </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -21966,6 +25436,11 @@
       <c r="G695" t="n">
         <v>10</v>
       </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -21997,6 +25472,11 @@
       <c r="G696" t="n">
         <v>12.61</v>
       </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -22028,6 +25508,11 @@
       <c r="G697" t="n">
         <v>12.61</v>
       </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -22059,6 +25544,11 @@
       <c r="G698" t="n">
         <v>12.01</v>
       </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -22090,6 +25580,11 @@
       <c r="G699" t="n">
         <v>12.01</v>
       </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -22121,6 +25616,11 @@
       <c r="G700" t="n">
         <v>12.01</v>
       </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -22152,6 +25652,11 @@
       <c r="G701" t="n">
         <v>9.01</v>
       </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -22183,6 +25688,11 @@
       <c r="G702" t="n">
         <v>8.109999999999999</v>
       </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
@@ -22214,6 +25724,11 @@
       <c r="G703" t="n">
         <v>6.01</v>
       </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
@@ -22245,6 +25760,11 @@
       <c r="G704" t="n">
         <v>6.01</v>
       </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
@@ -22276,6 +25796,11 @@
       <c r="G705" t="n">
         <v>6.01</v>
       </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -22307,6 +25832,11 @@
       <c r="G706" t="n">
         <v>3</v>
       </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -22338,6 +25868,11 @@
       <c r="G707" t="n">
         <v>0.6</v>
       </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -22369,6 +25904,11 @@
       <c r="G708" t="n">
         <v>13.49</v>
       </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -22400,6 +25940,11 @@
       <c r="G709" t="n">
         <v>12.46</v>
       </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -22431,6 +25976,11 @@
       <c r="G710" t="n">
         <v>12.46</v>
       </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -22462,6 +26012,11 @@
       <c r="G711" t="n">
         <v>12.46</v>
       </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -22493,6 +26048,11 @@
       <c r="G712" t="n">
         <v>11.07</v>
       </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -22524,6 +26084,11 @@
       <c r="G713" t="n">
         <v>11.07</v>
       </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -22555,6 +26120,11 @@
       <c r="G714" t="n">
         <v>8.300000000000001</v>
       </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -22586,6 +26156,11 @@
       <c r="G715" t="n">
         <v>8.300000000000001</v>
       </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -22617,6 +26192,11 @@
       <c r="G716" t="n">
         <v>6.23</v>
       </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -22648,6 +26228,11 @@
       <c r="G717" t="n">
         <v>3.46</v>
       </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -22679,6 +26264,11 @@
       <c r="G718" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -22710,6 +26300,11 @@
       <c r="G719" t="n">
         <v>45</v>
       </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -22741,6 +26336,11 @@
       <c r="G720" t="n">
         <v>40</v>
       </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -22772,6 +26372,11 @@
       <c r="G721" t="n">
         <v>15</v>
       </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -22803,6 +26408,11 @@
       <c r="G722" t="n">
         <v>15.76</v>
       </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -22834,6 +26444,11 @@
       <c r="G723" t="n">
         <v>15.76</v>
       </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -22865,6 +26480,11 @@
       <c r="G724" t="n">
         <v>14.71</v>
       </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
@@ -22896,6 +26516,11 @@
       <c r="G725" t="n">
         <v>12.18</v>
       </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
@@ -22927,6 +26552,11 @@
       <c r="G726" t="n">
         <v>6.3</v>
       </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="n">
@@ -22958,6 +26588,11 @@
       <c r="G727" t="n">
         <v>6.3</v>
       </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -22989,6 +26624,11 @@
       <c r="G728" t="n">
         <v>6.3</v>
       </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="n">
@@ -23020,6 +26660,11 @@
       <c r="G729" t="n">
         <v>6.3</v>
       </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="n">
@@ -23051,6 +26696,11 @@
       <c r="G730" t="n">
         <v>6.3</v>
       </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="n">
@@ -23082,6 +26732,11 @@
       <c r="G731" t="n">
         <v>6.3</v>
       </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
@@ -23113,6 +26768,11 @@
       <c r="G732" t="n">
         <v>3.15</v>
       </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="n">
@@ -23144,6 +26804,11 @@
       <c r="G733" t="n">
         <v>0.63</v>
       </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
@@ -23175,6 +26840,11 @@
       <c r="G734" t="n">
         <v>70</v>
       </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="n">
@@ -23206,6 +26876,11 @@
       <c r="G735" t="n">
         <v>19</v>
       </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="n">
@@ -23237,6 +26912,11 @@
       <c r="G736" t="n">
         <v>10</v>
       </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="n">
@@ -23268,6 +26948,11 @@
       <c r="G737" t="n">
         <v>1</v>
       </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="n">
@@ -23299,6 +26984,11 @@
       <c r="G738" t="n">
         <v>36.36</v>
       </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
@@ -23330,6 +27020,11 @@
       <c r="G739" t="n">
         <v>21.82</v>
       </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
@@ -23361,6 +27056,11 @@
       <c r="G740" t="n">
         <v>18.18</v>
       </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
@@ -23392,6 +27092,11 @@
       <c r="G741" t="n">
         <v>9.09</v>
       </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
@@ -23423,6 +27128,11 @@
       <c r="G742" t="n">
         <v>9.09</v>
       </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
@@ -23454,6 +27164,11 @@
       <c r="G743" t="n">
         <v>4.55</v>
       </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="n">
@@ -23485,6 +27200,11 @@
       <c r="G744" t="n">
         <v>0.91</v>
       </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="n">
@@ -23516,6 +27236,11 @@
       <c r="G745" t="n">
         <v>16.67</v>
       </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="n">
@@ -23547,6 +27272,11 @@
       <c r="G746" t="n">
         <v>16.67</v>
       </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="n">
@@ -23578,6 +27308,11 @@
       <c r="G747" t="n">
         <v>16.67</v>
       </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="n">
@@ -23609,6 +27344,11 @@
       <c r="G748" t="n">
         <v>16.67</v>
       </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="n">
@@ -23640,6 +27380,11 @@
       <c r="G749" t="n">
         <v>16.67</v>
       </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="n">
@@ -23671,6 +27416,11 @@
       <c r="G750" t="n">
         <v>15.83</v>
       </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="n">
@@ -23702,6 +27452,11 @@
       <c r="G751" t="n">
         <v>0.83</v>
       </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="n">
@@ -23733,6 +27488,11 @@
       <c r="G752" t="n">
         <v>36.36</v>
       </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
@@ -23764,6 +27524,11 @@
       <c r="G753" t="n">
         <v>21.82</v>
       </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="n">
@@ -23795,6 +27560,11 @@
       <c r="G754" t="n">
         <v>18.18</v>
       </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
@@ -23826,6 +27596,11 @@
       <c r="G755" t="n">
         <v>9.09</v>
       </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
@@ -23857,6 +27632,11 @@
       <c r="G756" t="n">
         <v>9.09</v>
       </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="n">
@@ -23888,6 +27668,11 @@
       <c r="G757" t="n">
         <v>4.55</v>
       </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="n">
@@ -23919,6 +27704,11 @@
       <c r="G758" t="n">
         <v>0.91</v>
       </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="n">
@@ -23950,6 +27740,11 @@
       <c r="G759" t="n">
         <v>30</v>
       </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="n">
@@ -23981,6 +27776,11 @@
       <c r="G760" t="n">
         <v>30</v>
       </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="n">
@@ -24012,6 +27812,11 @@
       <c r="G761" t="n">
         <v>20</v>
       </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="n">
@@ -24043,6 +27848,11 @@
       <c r="G762" t="n">
         <v>15</v>
       </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="n">
@@ -24074,6 +27884,11 @@
       <c r="G763" t="n">
         <v>5</v>
       </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="n">
@@ -24105,6 +27920,11 @@
       <c r="G764" t="n">
         <v>24.19</v>
       </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="n">
@@ -24136,6 +27956,11 @@
       <c r="G765" t="n">
         <v>23.72</v>
       </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="n">
@@ -24167,6 +27992,11 @@
       <c r="G766" t="n">
         <v>13.95</v>
       </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="n">
@@ -24198,6 +28028,11 @@
       <c r="G767" t="n">
         <v>13.95</v>
       </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="n">
@@ -24229,6 +28064,11 @@
       <c r="G768" t="n">
         <v>13.95</v>
       </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
@@ -24260,6 +28100,11 @@
       <c r="G769" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
@@ -24291,6 +28136,11 @@
       <c r="G770" t="n">
         <v>0.93</v>
       </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="n">
@@ -24322,6 +28172,11 @@
       <c r="G771" t="n">
         <v>13.66</v>
       </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
@@ -24353,6 +28208,11 @@
       <c r="G772" t="n">
         <v>13.66</v>
       </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="n">
@@ -24384,6 +28244,11 @@
       <c r="G773" t="n">
         <v>13.66</v>
       </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="n">
@@ -24415,6 +28280,11 @@
       <c r="G774" t="n">
         <v>13.11</v>
       </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="n">
@@ -24446,6 +28316,11 @@
       <c r="G775" t="n">
         <v>12.57</v>
       </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="n">
@@ -24477,6 +28352,11 @@
       <c r="G776" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="n">
@@ -24508,6 +28388,11 @@
       <c r="G777" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="n">
@@ -24539,6 +28424,11 @@
       <c r="G778" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="n">
@@ -24570,6 +28460,11 @@
       <c r="G779" t="n">
         <v>5.46</v>
       </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
@@ -24601,6 +28496,11 @@
       <c r="G780" t="n">
         <v>2.73</v>
       </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
@@ -24632,6 +28532,11 @@
       <c r="G781" t="n">
         <v>0.55</v>
       </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="n">
@@ -24663,6 +28568,11 @@
       <c r="G782" t="n">
         <v>15</v>
       </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="n">
@@ -24694,6 +28604,11 @@
       <c r="G783" t="n">
         <v>12.5</v>
       </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="n">
@@ -24725,6 +28640,11 @@
       <c r="G784" t="n">
         <v>12.5</v>
       </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
@@ -24756,6 +28676,11 @@
       <c r="G785" t="n">
         <v>12.5</v>
       </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
@@ -24787,6 +28712,11 @@
       <c r="G786" t="n">
         <v>12.5</v>
       </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
@@ -24818,6 +28748,11 @@
       <c r="G787" t="n">
         <v>10</v>
       </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
@@ -24849,6 +28784,11 @@
       <c r="G788" t="n">
         <v>10</v>
       </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
@@ -24880,6 +28820,11 @@
       <c r="G789" t="n">
         <v>7.5</v>
       </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="n">
@@ -24911,6 +28856,11 @@
       <c r="G790" t="n">
         <v>5</v>
       </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
@@ -24942,6 +28892,11 @@
       <c r="G791" t="n">
         <v>2</v>
       </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
@@ -24973,6 +28928,11 @@
       <c r="G792" t="n">
         <v>0.5</v>
       </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
@@ -25004,6 +28964,11 @@
       <c r="G793" t="n">
         <v>60</v>
       </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="n">
@@ -25035,6 +29000,11 @@
       <c r="G794" t="n">
         <v>30</v>
       </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="n">
@@ -25066,6 +29036,11 @@
       <c r="G795" t="n">
         <v>10</v>
       </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
@@ -25097,6 +29072,11 @@
       <c r="G796" t="n">
         <v>100</v>
       </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
@@ -25128,6 +29108,11 @@
       <c r="G797" t="n">
         <v>50</v>
       </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
@@ -25159,6 +29144,11 @@
       <c r="G798" t="n">
         <v>50</v>
       </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
@@ -25190,6 +29180,11 @@
       <c r="G799" t="n">
         <v>18.18</v>
       </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
@@ -25221,6 +29216,11 @@
       <c r="G800" t="n">
         <v>18.18</v>
       </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
@@ -25252,6 +29252,11 @@
       <c r="G801" t="n">
         <v>13.64</v>
       </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
@@ -25283,6 +29288,11 @@
       <c r="G802" t="n">
         <v>13.64</v>
       </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
@@ -25314,6 +29324,11 @@
       <c r="G803" t="n">
         <v>9.09</v>
       </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="n">
@@ -25345,6 +29360,11 @@
       <c r="G804" t="n">
         <v>9.09</v>
       </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -25376,6 +29396,11 @@
       <c r="G805" t="n">
         <v>9.09</v>
       </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="n">
@@ -25407,6 +29432,11 @@
       <c r="G806" t="n">
         <v>8.18</v>
       </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="n">
@@ -25438,6 +29468,11 @@
       <c r="G807" t="n">
         <v>0.91</v>
       </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="n">
@@ -25469,6 +29504,11 @@
       <c r="G808" t="n">
         <v>80</v>
       </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="n">
@@ -25500,6 +29540,11 @@
       <c r="G809" t="n">
         <v>20</v>
       </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
@@ -25531,6 +29576,11 @@
       <c r="G810" t="n">
         <v>20</v>
       </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="n">
@@ -25562,6 +29612,11 @@
       <c r="G811" t="n">
         <v>20</v>
       </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="n">
@@ -25593,6 +29648,11 @@
       <c r="G812" t="n">
         <v>20</v>
       </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="n">
@@ -25624,6 +29684,11 @@
       <c r="G813" t="n">
         <v>15</v>
       </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
@@ -25655,6 +29720,11 @@
       <c r="G814" t="n">
         <v>15</v>
       </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
@@ -25686,6 +29756,11 @@
       <c r="G815" t="n">
         <v>10</v>
       </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
@@ -25717,6 +29792,11 @@
       <c r="G816" t="n">
         <v>12.05</v>
       </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
@@ -25748,6 +29828,11 @@
       <c r="G817" t="n">
         <v>12.05</v>
       </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
@@ -25779,6 +29864,11 @@
       <c r="G818" t="n">
         <v>12.05</v>
       </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
@@ -25810,6 +29900,11 @@
       <c r="G819" t="n">
         <v>12.05</v>
       </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="n">
@@ -25841,6 +29936,11 @@
       <c r="G820" t="n">
         <v>10.84</v>
       </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
@@ -25872,6 +29972,11 @@
       <c r="G821" t="n">
         <v>7.23</v>
       </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
@@ -25903,6 +30008,11 @@
       <c r="G822" t="n">
         <v>6.75</v>
       </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
@@ -25934,6 +30044,11 @@
       <c r="G823" t="n">
         <v>4.82</v>
       </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
@@ -25965,6 +30080,11 @@
       <c r="G824" t="n">
         <v>4.82</v>
       </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
@@ -25996,6 +30116,11 @@
       <c r="G825" t="n">
         <v>4.82</v>
       </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="n">
@@ -26027,6 +30152,11 @@
       <c r="G826" t="n">
         <v>4.82</v>
       </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
@@ -26058,6 +30188,11 @@
       <c r="G827" t="n">
         <v>4.82</v>
       </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="n">
@@ -26089,6 +30224,11 @@
       <c r="G828" t="n">
         <v>2.41</v>
       </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="n">
@@ -26119,6 +30259,11 @@
       </c>
       <c r="G829" t="n">
         <v>0.48</v>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
   </sheetData>
